--- a/public/exemplos/questoes-exemplo.xlsx
+++ b/public/exemplos/questoes-exemplo.xlsx
@@ -188,37 +188,57 @@
         <t>Obrigatório. A alternativa correta (aceita "Resposta", "Alternativa", "Letra" ou "Correta" como nome da coluna).</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Opcional. Área do conhecimento cobrada pela questão. Um valor por questão.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Opcional. Tema/assunto específico dentro da área. Um valor por questão.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Opcional. Habilidade/competência avaliada. Um valor por questão.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Opcional. Também aceita o cabeçalho "Taxonomia" (ex.: Lembrar, Aplicar, Analisar, Avaliar).</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <t>Opcional. Aceita vários valores na mesma célula, separados por ";", "," ou "|".</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <t>Opcional. Aceita vários valores na mesma célula, separados por ";", "," ou "|".</t>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <t>Opcional. Aceita vários valores na mesma célula, separados por ";", "," ou "|".</t>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
+    <comment ref="N1" authorId="0" shapeId="0">
       <text>
         <t>Opcional. Um valor por célula (use as colunas B/C ao lado para mais de um).</t>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
+    <comment ref="Q1" authorId="0" shapeId="0">
       <text>
         <t>Opcional. Um valor por célula (use a coluna B ao lado para mais de um).</t>
       </text>
     </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
+    <comment ref="S1" authorId="0" shapeId="0">
       <text>
         <t>Opcional. Um valor por célula (use as colunas B/C ao lado para mais de um).</t>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
+    <comment ref="V1" authorId="0" shapeId="0">
       <text>
         <t>Opcional. Um valor por célula (use as colunas B/C/D ao lado para mais de um).</t>
       </text>
@@ -516,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -560,19 +580,33 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>"Matriz (período)", "Matriz (disciplina)" e "Matriz (código)" aceitam mais de um valor na mesma célula, separados por ";", "," ou "|" (ver linha 2 do exemplo).</t>
+          <t>Área, Tema e Habilidade são um valor só por questão (igual Bloom/Miller/Dificuldade) — descrevem o conteúdo cobrado por aquela questão.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>"Bloom (verbo)" também aceita o cabeçalho "Taxonomia" — se sua planilha já usa esse nome com os verbos de Bloom (Lembrar, Aplicar, Analisar, Avaliar...), não precisa renomear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>"Matriz (período)", "Matriz (disciplina)" e "Matriz (código)" aceitam mais de um valor na mesma célula, separados por ";", "," ou "|" (ver linha 2 do exemplo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>Reimportar o mesmo número de questão desta prova atualiza os dados em vez de duplicar — então também serve para corrigir um gabarito depois.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Aceita .xlsx, .xls ou .csv.</t>
         </is>
@@ -589,31 +623,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
-    <col width="19" customWidth="1" min="17" max="17"/>
-    <col width="19" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -629,100 +666,115 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
+          <t>Área</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Tema</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Habilidade</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
           <t>Bloom (nível)</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Bloom (verbo)</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Miller (nível)</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Dificuldade Pedagógica</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Dificuldade TRI</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Matriz (período)</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>Matriz (disciplina)</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Matriz (código)</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>Matriz Prova A</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>Matriz Prova B</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>Matriz Prova C</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>DCN A</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>DCN B</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>Portaria INEP A</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>Portaria INEP B</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>Portaria INEP C</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="V1" s="4" t="inlineStr">
         <is>
           <t>PPC A</t>
         </is>
       </c>
-      <c r="T1" s="4" t="inlineStr">
+      <c r="W1" s="4" t="inlineStr">
         <is>
           <t>PPC B</t>
         </is>
       </c>
-      <c r="U1" s="4" t="inlineStr">
+      <c r="X1" s="4" t="inlineStr">
         <is>
           <t>PPC C</t>
         </is>
       </c>
-      <c r="V1" s="4" t="inlineStr">
+      <c r="Y1" s="4" t="inlineStr">
         <is>
           <t>PPC D</t>
         </is>
@@ -739,82 +791,97 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Aplicar</t>
+          <t>Clínica Médica</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Diagnosticar</t>
+          <t>HIV/AIDS</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>E3 — Avaliação e Julgamento Ético-Profissional</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Aplicação</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Avaliar</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
           <t>Sabe como</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>facil</t>
         </is>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="J2" s="5" t="n">
         <v>0.35</v>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>1;2</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>Anatomia;Fisiologia</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>AN01;FI02</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>Item 1</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="O2" s="5" t="inlineStr">
         <is>
           <t>Item 2</t>
         </is>
       </c>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="P2" s="5" t="n"/>
+      <c r="Q2" s="5" t="inlineStr">
         <is>
           <t>Art. 5º</t>
-        </is>
-      </c>
-      <c r="O2" s="5" t="n"/>
-      <c r="P2" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="Q2" s="5" t="inlineStr">
-        <is>
-          <t>P2</t>
         </is>
       </c>
       <c r="R2" s="5" t="n"/>
       <c r="S2" s="5" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="n"/>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
           <t>PPC-01</t>
         </is>
       </c>
-      <c r="T2" s="5" t="inlineStr">
+      <c r="W2" s="5" t="inlineStr">
         <is>
           <t>PPC-02</t>
         </is>
       </c>
-      <c r="U2" s="5" t="n"/>
-      <c r="V2" s="5" t="n"/>
+      <c r="X2" s="5" t="n"/>
+      <c r="Y2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -827,62 +894,77 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
+          <t>Cirurgia Geral</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Cirurgia Bariátrica</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>E2 — Aplicação e Análise</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Análise</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
           <t>Analisar</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Comparar</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Sabe fazer</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>medio</t>
         </is>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="J3" s="5" t="n">
         <v>0.58</v>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>Clínica Médica</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>CM04</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>Item 3</t>
         </is>
       </c>
-      <c r="L3" s="5" t="n"/>
-      <c r="M3" s="5" t="n"/>
-      <c r="N3" s="5" t="n"/>
       <c r="O3" s="5" t="n"/>
       <c r="P3" s="5" t="n"/>
       <c r="Q3" s="5" t="n"/>
       <c r="R3" s="5" t="n"/>
-      <c r="S3" s="5" t="inlineStr">
-        <is>
-          <t>PPC-03</t>
-        </is>
-      </c>
+      <c r="S3" s="5" t="n"/>
       <c r="T3" s="5" t="n"/>
       <c r="U3" s="5" t="n"/>
-      <c r="V3" s="5" t="n"/>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>PPC-03</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="n"/>
+      <c r="X3" s="5" t="n"/>
+      <c r="Y3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
@@ -913,6 +995,9 @@
       <c r="T4" s="5" t="n"/>
       <c r="U4" s="5" t="n"/>
       <c r="V4" s="5" t="n"/>
+      <c r="W4" s="5" t="n"/>
+      <c r="X4" s="5" t="n"/>
+      <c r="Y4" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
